--- a/artfynd/A 26767-2026 artfynd.xlsx
+++ b/artfynd/A 26767-2026 artfynd.xlsx
@@ -5129,10 +5129,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133575927</v>
+        <v>133575929</v>
       </c>
       <c r="B43" t="n">
-        <v>83344</v>
+        <v>91960</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,21 +5140,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407892</v>
+        <v>407915</v>
       </c>
       <c r="R43" t="n">
-        <v>6780260</v>
+        <v>6780235</v>
       </c>
       <c r="S43" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5236,10 +5236,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133575929</v>
+        <v>133575927</v>
       </c>
       <c r="B44" t="n">
-        <v>91960</v>
+        <v>83344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5271,13 +5271,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407915</v>
+        <v>407892</v>
       </c>
       <c r="R44" t="n">
-        <v>6780235</v>
+        <v>6780260</v>
       </c>
       <c r="S44" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6199,32 +6199,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133575925</v>
+        <v>133575931</v>
       </c>
       <c r="B53" t="n">
-        <v>91974</v>
+        <v>92304</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6234,13 +6234,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408012</v>
+        <v>407902</v>
       </c>
       <c r="R53" t="n">
-        <v>6780284</v>
+        <v>6780216</v>
       </c>
       <c r="S53" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6306,10 +6306,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133575928</v>
+        <v>133575938</v>
       </c>
       <c r="B54" t="n">
-        <v>97421</v>
+        <v>91974</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407930</v>
+        <v>407833</v>
       </c>
       <c r="R54" t="n">
-        <v>6780196</v>
+        <v>6780214</v>
       </c>
       <c r="S54" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6413,10 +6413,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133575938</v>
+        <v>133575928</v>
       </c>
       <c r="B55" t="n">
-        <v>91974</v>
+        <v>97421</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,21 +6424,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6448,13 +6448,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407833</v>
+        <v>407930</v>
       </c>
       <c r="R55" t="n">
-        <v>6780214</v>
+        <v>6780196</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6520,32 +6520,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133575931</v>
+        <v>133575925</v>
       </c>
       <c r="B56" t="n">
-        <v>92304</v>
+        <v>91974</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407902</v>
+        <v>408012</v>
       </c>
       <c r="R56" t="n">
-        <v>6780216</v>
+        <v>6780284</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134035681</v>
+        <v>134035765</v>
       </c>
       <c r="B58" t="n">
-        <v>92304</v>
+        <v>92392</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407938</v>
+        <v>407960</v>
       </c>
       <c r="R58" t="n">
-        <v>6780225</v>
+        <v>6780204</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134035765</v>
+        <v>134035681</v>
       </c>
       <c r="B60" t="n">
-        <v>92392</v>
+        <v>92304</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>2062</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407960</v>
+        <v>407938</v>
       </c>
       <c r="R60" t="n">
-        <v>6780204</v>
+        <v>6780225</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7162,32 +7162,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134035773</v>
+        <v>134035692</v>
       </c>
       <c r="B62" t="n">
-        <v>98046</v>
+        <v>91960</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407861</v>
+        <v>407842</v>
       </c>
       <c r="R62" t="n">
-        <v>6780349</v>
+        <v>6780217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7269,7 +7269,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134035770</v>
+        <v>134035773</v>
       </c>
       <c r="B63" t="n">
         <v>98046</v>
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408040</v>
+        <v>407861</v>
       </c>
       <c r="R63" t="n">
-        <v>6780216</v>
+        <v>6780349</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7376,32 +7376,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134035692</v>
+        <v>134035770</v>
       </c>
       <c r="B64" t="n">
-        <v>91960</v>
+        <v>98046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407842</v>
+        <v>408040</v>
       </c>
       <c r="R64" t="n">
-        <v>6780217</v>
+        <v>6780216</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7809,32 +7809,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134035687</v>
+        <v>134035683</v>
       </c>
       <c r="B68" t="n">
-        <v>91960</v>
+        <v>92304</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407938</v>
+        <v>407893</v>
       </c>
       <c r="R68" t="n">
-        <v>6780225</v>
+        <v>6780206</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7916,32 +7916,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134035683</v>
+        <v>134035687</v>
       </c>
       <c r="B69" t="n">
-        <v>92304</v>
+        <v>91960</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407893</v>
+        <v>407938</v>
       </c>
       <c r="R69" t="n">
-        <v>6780206</v>
+        <v>6780225</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8023,7 +8023,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134035864</v>
+        <v>134035881</v>
       </c>
       <c r="B70" t="n">
         <v>79359</v>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407680</v>
+        <v>407653</v>
       </c>
       <c r="R70" t="n">
-        <v>6780305</v>
+        <v>6780262</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8130,7 +8130,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134035881</v>
+        <v>134035864</v>
       </c>
       <c r="B71" t="n">
         <v>79359</v>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407653</v>
+        <v>407680</v>
       </c>
       <c r="R71" t="n">
-        <v>6780262</v>
+        <v>6780305</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8237,45 +8237,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134035673</v>
+        <v>134035740</v>
       </c>
       <c r="B72" t="n">
-        <v>91923</v>
+        <v>57972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408024</v>
+        <v>407962</v>
       </c>
       <c r="R72" t="n">
-        <v>6780235</v>
+        <v>6780206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8307,7 +8312,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8317,7 +8322,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8344,50 +8349,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134035740</v>
+        <v>134035673</v>
       </c>
       <c r="B73" t="n">
-        <v>57972</v>
+        <v>91923</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407962</v>
+        <v>408024</v>
       </c>
       <c r="R73" t="n">
-        <v>6780206</v>
+        <v>6780235</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8675,10 +8675,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134035930</v>
+        <v>134035772</v>
       </c>
       <c r="B76" t="n">
-        <v>5181</v>
+        <v>98046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8686,39 +8686,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407897</v>
+        <v>407788</v>
       </c>
       <c r="R76" t="n">
-        <v>6780217</v>
+        <v>6780342</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,7 +8745,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8760,7 +8755,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8787,10 +8782,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134035772</v>
+        <v>134035930</v>
       </c>
       <c r="B77" t="n">
-        <v>98046</v>
+        <v>5181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8798,34 +8793,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407788</v>
+        <v>407897</v>
       </c>
       <c r="R77" t="n">
-        <v>6780342</v>
+        <v>6780217</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 26767-2026 artfynd.xlsx
+++ b/artfynd/A 26767-2026 artfynd.xlsx
@@ -6630,7 +6630,7 @@
         <v>134035689</v>
       </c>
       <c r="B57" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>134035765</v>
       </c>
       <c r="B58" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>134035714</v>
       </c>
       <c r="B59" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>134035681</v>
       </c>
       <c r="B60" t="n">
-        <v>92304</v>
+        <v>92311</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>134035880</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7162,32 +7162,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134035692</v>
+        <v>134035770</v>
       </c>
       <c r="B62" t="n">
-        <v>91960</v>
+        <v>98053</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407842</v>
+        <v>408040</v>
       </c>
       <c r="R62" t="n">
-        <v>6780217</v>
+        <v>6780216</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7272,7 +7272,7 @@
         <v>134035773</v>
       </c>
       <c r="B63" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7376,32 +7376,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134035770</v>
+        <v>134035692</v>
       </c>
       <c r="B64" t="n">
-        <v>98046</v>
+        <v>91967</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408040</v>
+        <v>407842</v>
       </c>
       <c r="R64" t="n">
-        <v>6780216</v>
+        <v>6780217</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7486,7 +7486,7 @@
         <v>134035738</v>
       </c>
       <c r="B65" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>134035882</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>134035683</v>
       </c>
       <c r="B68" t="n">
-        <v>92304</v>
+        <v>92311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>134035687</v>
       </c>
       <c r="B69" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8023,10 +8023,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134035881</v>
+        <v>134035864</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407653</v>
+        <v>407680</v>
       </c>
       <c r="R70" t="n">
-        <v>6780262</v>
+        <v>6780305</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8130,10 +8130,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134035864</v>
+        <v>134035881</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407680</v>
+        <v>407653</v>
       </c>
       <c r="R71" t="n">
-        <v>6780305</v>
+        <v>6780262</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8237,50 +8237,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134035740</v>
+        <v>134035673</v>
       </c>
       <c r="B72" t="n">
-        <v>57972</v>
+        <v>91930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407962</v>
+        <v>408024</v>
       </c>
       <c r="R72" t="n">
-        <v>6780206</v>
+        <v>6780235</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8312,7 +8307,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8322,7 +8317,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8349,45 +8344,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134035673</v>
+        <v>134035740</v>
       </c>
       <c r="B73" t="n">
-        <v>91923</v>
+        <v>57972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408024</v>
+        <v>407962</v>
       </c>
       <c r="R73" t="n">
-        <v>6780235</v>
+        <v>6780206</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8571,7 +8571,7 @@
         <v>134035739</v>
       </c>
       <c r="B75" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>134035772</v>
       </c>
       <c r="B76" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>134035691</v>
       </c>
       <c r="B78" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>134035690</v>
       </c>
       <c r="B79" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>134035766</v>
       </c>
       <c r="B80" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26767-2026 artfynd.xlsx
+++ b/artfynd/A 26767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AZ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575940</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575933</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62864545</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84682928</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575929</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575932</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035687</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035689</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035690</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035691</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035692</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035707</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575925</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575937</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575938</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62864553</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84682931</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575936</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3016,6 +3126,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035765</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035766</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575924</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575931</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035681</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035683</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035804</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035805</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3872,6 +4022,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035806</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035808</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035826</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,6 +4358,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035827</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4300,6 +4470,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035712</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4407,6 +4582,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575942</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4508,6 +4688,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84682862</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4609,6 +4794,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84682879</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4710,6 +4900,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84682935</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4817,6 +5012,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461665</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4924,6 +5124,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461666</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5031,6 +5236,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575934</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5138,6 +5348,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035673</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5245,6 +5460,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461694</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5352,6 +5572,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461695</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5459,6 +5684,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461696</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5566,6 +5796,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461697</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5673,6 +5908,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461698</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5780,6 +6020,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461699</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5887,6 +6132,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461700</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5994,6 +6244,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461701</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6101,6 +6356,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461702</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6208,6 +6468,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461703</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6315,6 +6580,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461704</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6422,6 +6692,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461705</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6529,6 +6804,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461706</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6636,6 +6916,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461707</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6743,6 +7028,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461708</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6850,6 +7140,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461709</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6957,6 +7252,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461710</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7064,6 +7364,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461711</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7171,6 +7476,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461712</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7278,6 +7588,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461713</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7385,6 +7700,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461714</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7492,6 +7812,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461715</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7599,6 +7924,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035864</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7706,6 +8036,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035880</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7813,6 +8148,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035881</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7920,6 +8260,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035882</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8027,6 +8372,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461661</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8134,6 +8484,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461662</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8241,6 +8596,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461663</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8348,6 +8708,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461664</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8455,6 +8820,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575927</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8554,6 +8924,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63561471</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8671,6 +9046,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461672</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8783,6 +9163,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461674</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8895,6 +9280,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461675</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9007,6 +9397,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035740</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9124,6 +9519,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461677</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9241,6 +9641,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461680</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9353,6 +9758,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461726</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9465,6 +9875,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461727</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9577,6 +9992,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461728</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9689,6 +10109,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461729</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9801,6 +10226,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461730</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9913,6 +10343,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461731</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10030,6 +10465,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035764</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10142,6 +10582,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035884</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10254,6 +10699,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035885</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10360,6 +10810,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62864731</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10472,6 +10927,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131461736</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10584,6 +11044,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035930</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10691,6 +11156,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035856</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10798,6 +11268,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035924</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10905,6 +11380,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035927</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11012,6 +11492,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035770</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11119,6 +11604,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035772</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11226,6 +11716,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035773</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11333,6 +11828,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035737</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11440,6 +11940,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035738</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11547,6 +12052,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035739</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11654,6 +12164,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035714</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11761,6 +12276,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035774</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11868,6 +12388,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035775</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11975,6 +12500,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035776</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12082,6 +12612,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035777</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12189,6 +12724,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035779</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12296,6 +12836,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035780</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12403,6 +12948,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035781</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12510,6 +13060,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035782</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12617,6 +13172,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035797</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12724,6 +13284,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035798</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12831,6 +13396,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035799</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12938,8 +13508,129 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>